--- a/output_manual/manual_bom.xlsx
+++ b/output_manual/manual_bom.xlsx
@@ -622,12 +622,12 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>GR-005</t>
+          <t>GR-002</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Custom_Stair_Step</t>
+          <t>Spur_Gear_3D</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -647,10 +647,8 @@
       <c r="H4" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I4" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>

--- a/output_manual/manual_bom.xlsx
+++ b/output_manual/manual_bom.xlsx
@@ -29,7 +29,7 @@
       <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="00F0B429"/>
-      <sz val="12"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -515,21 +515,21 @@
     <col width="10" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SIRAAL 3D GEAR ENGINE — GEAR BILL OF MATERIALS</t>
+          <t>SIRAAL 3D GEAR ENGINE — BILL OF MATERIALS</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1">
+    <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>IS 2535 / ISO 1328  |  Involute 20°  |  1st Angle  |  TN-IMPACT 2026  |  P1=Teeth Z (N_starts for Worm)  P2=Module m(mm)  P3=Face Width(mm)  P4=Bore Dia(mm) or Ring Thk</t>
+          <t>IS 2535 / ISO 1328  |  Involute 20°  |  TN-IMPACT 2026  |  1st Angle Projection</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1">
+    <row r="3" ht="28" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>#</t>
@@ -552,26 +552,22 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Param_1
-(Z / Starts)</t>
+          <t>Param_1</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Param_2
-(Module m)</t>
+          <t>Param_2</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Param_3
-(Face Width)</t>
+          <t>Param_3</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Param_4
-(Bore Dia)</t>
+          <t>Param_4</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -601,8 +597,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>Est_Cost
-(Rs)</t>
+          <t>Est_Cost_Rs</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -622,12 +617,12 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>GR-002</t>
+          <t>GR-005</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Spur_Gear_3D</t>
+          <t>Custom_V8_Engine_Block</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -636,16 +631,16 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>20</v>
+        <v>600</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>3</v>
+        <v>280</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>30</v>
+        <v>380</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="I4" s="4" t="n">
         <v>1</v>
@@ -662,10 +657,10 @@
       </c>
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="n">
-        <v>0.001</v>
+        <v>61240.658</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>0.18</v>
+        <v>11329521.73</v>
       </c>
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="4" t="n">

--- a/output_manual/manual_bom.xlsx
+++ b/output_manual/manual_bom.xlsx
@@ -617,12 +617,12 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>GR-005</t>
+          <t>GR-002</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Custom_V8_Engine_Block</t>
+          <t>Custom_v8_engine</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>600</v>
+        <v>92</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>280</v>
+        <v>86</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>380</v>
+        <v>120</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="I4" s="4" t="n">
         <v>1</v>
@@ -657,10 +657,10 @@
       </c>
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="n">
-        <v>61240.658</v>
+        <v>44.482</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>11329521.73</v>
+        <v>8229.17</v>
       </c>
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="4" t="n">
